--- a/data/raw/2026/9月/展览.xlsx
+++ b/data/raw/2026/9月/展览.xlsx
@@ -1312,14 +1312,14 @@
     <col width="5.19090909090909" customWidth="1" style="3" min="92" max="92"/>
     <col width="5.44545454545455" customWidth="1" style="3" min="93" max="93"/>
     <col width="20.5181818181818" customWidth="1" style="3" min="94" max="95"/>
-    <col width="100.890909090909" customWidth="1" style="3" min="96" max="96"/>
+    <col width="100.9" customWidth="1" style="3" min="96" max="96"/>
     <col width="9.072727272727271" customWidth="1" style="3" min="97" max="97"/>
     <col width="20.5181818181818" customWidth="1" style="3" min="98" max="98"/>
     <col width="9.31818181818182" customWidth="1" style="3" min="99" max="99"/>
     <col width="10.4181818181818" customWidth="1" style="3" min="100" max="100"/>
     <col width="14.4545454545455" customWidth="1" style="3" min="101" max="101"/>
     <col width="7.64545454545455" customWidth="1" style="3" min="102" max="102"/>
-    <col width="50.7181818181818" customWidth="1" style="3" min="103" max="103"/>
+    <col width="48.4" customWidth="1" style="3" min="103" max="103"/>
     <col width="7.70909090909091" customWidth="1" style="3" min="104" max="104"/>
     <col width="23.0454545454545" customWidth="1" style="3" min="105" max="105"/>
   </cols>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1888,36 +1888,48 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>动漫周边</t>
+          <t>2026 浙江跨境电商产业带及区域合作展&amp;杭州出口跨境电商博览会</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>参展商</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2-4次</t>
-        </is>
-      </c>
+          <t>展览主承办</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10001人以上</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>5次以上</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>46-55岁</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -1927,19 +1939,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -1947,8 +1959,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -1969,26 +1989,58 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2019,14 +2071,46 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AY2" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AZ2" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
       <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2037,18 +2121,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BC2" s="2" t="inlineStr"/>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr"/>
-      <c r="BF2" s="2" t="inlineStr"/>
+      <c r="BC2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BD2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BG2" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI2" s="2" t="inlineStr">
@@ -2068,7 +2168,7 @@
       </c>
       <c r="BL2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BM2" s="2" t="inlineStr">
@@ -2078,19 +2178,11 @@
       </c>
       <c r="BN2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BO2" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BP2" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr"/>
+      <c r="BP2" s="2" t="inlineStr"/>
       <c r="BQ2" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -2121,23 +2213,31 @@
       <c r="CB2" s="2" t="inlineStr"/>
       <c r="CC2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">超出预期	</t>
-        </is>
-      </c>
-      <c r="CE2" s="2" t="inlineStr"/>
-      <c r="CF2" s="2" t="inlineStr"/>
+          <t xml:space="preserve">达到预期	</t>
+        </is>
+      </c>
+      <c r="CE2" s="2" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="CG2" s="2" t="inlineStr"/>
-      <c r="CH2" s="2" t="inlineStr"/>
-      <c r="CI2" s="2" t="inlineStr">
+      <c r="CH2" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
+      <c r="CI2" s="2" t="inlineStr"/>
       <c r="CJ2" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -2145,7 +2245,7 @@
       </c>
       <c r="CK2" s="2" t="inlineStr">
         <is>
-          <t>空调温度可以调低一点</t>
+          <t>地下车库标识标牌需要增设；场馆网 络收费价格偏高；商务简餐口味一般且定价偏高。</t>
         </is>
       </c>
       <c r="CL2" s="2" t="inlineStr"/>
@@ -2153,29 +2253,17 @@
       <c r="CN2" s="2" t="inlineStr"/>
       <c r="CO2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:53:15</t>
+          <t>2026-10-09 12:00:53</t>
         </is>
       </c>
       <c r="CP2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:53:15</t>
-        </is>
-      </c>
-      <c r="CQ2" s="2" t="inlineStr">
-        <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/150c94ad48da4b219dfdee6302e5c38b.mp3</t>
-        </is>
-      </c>
-      <c r="CR2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 分 15 秒 </t>
-        </is>
-      </c>
-      <c r="CS2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 14:48:58</t>
-        </is>
-      </c>
+          <t>2026-10-09 12:00:53</t>
+        </is>
+      </c>
+      <c r="CQ2" s="2" t="inlineStr"/>
+      <c r="CR2" s="2" t="inlineStr"/>
+      <c r="CS2" s="2" t="inlineStr"/>
       <c r="CT2" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2186,26 +2274,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV2" s="2" t="inlineStr">
-        <is>
-          <t>0,323,324,326</t>
-        </is>
-      </c>
+      <c r="CV2" s="2" t="inlineStr"/>
       <c r="CW2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX2" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市萧山区盈丰街道利一路奥景名邸</t>
-        </is>
-      </c>
-      <c r="CY2" s="2" t="inlineStr">
-        <is>
-          <t>杭博访问员2</t>
-        </is>
-      </c>
+      <c r="CX2" s="2" t="inlineStr"/>
+      <c r="CY2" s="2" t="inlineStr"/>
       <c r="CZ2" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -2225,7 +2301,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2240,21 +2316,25 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>动漫周边</t>
+          <t>2026 CBE 杭州国际美容博览会</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>参展商</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+          <t>展览主承办</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>10001人以上</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2-4次</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>女</t>
@@ -2265,11 +2345,19 @@
           <t>26-35岁</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -2279,12 +2367,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -2299,11 +2387,19 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -2321,26 +2417,58 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2371,17 +2499,49 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AY3" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AZ3" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
       <c r="BA3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB3" s="2" t="inlineStr">
@@ -2389,18 +2549,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BC3" s="2" t="inlineStr"/>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr"/>
-      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BC3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BD3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BE3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BG3" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI3" s="2" t="inlineStr">
@@ -2433,16 +2609,8 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BO3" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BP3" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="BO3" s="2" t="inlineStr"/>
+      <c r="BP3" s="2" t="inlineStr"/>
       <c r="BQ3" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -2473,57 +2641,57 @@
       <c r="CB3" s="2" t="inlineStr"/>
       <c r="CC3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">超出预期	</t>
-        </is>
-      </c>
-      <c r="CE3" s="2" t="inlineStr"/>
-      <c r="CF3" s="2" t="inlineStr"/>
+          <t xml:space="preserve">达到预期	</t>
+        </is>
+      </c>
+      <c r="CE3" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="CF3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="CG3" s="2" t="inlineStr"/>
-      <c r="CH3" s="2" t="inlineStr"/>
-      <c r="CI3" s="2" t="inlineStr">
+      <c r="CH3" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
+      <c r="CI3" s="2" t="inlineStr"/>
       <c r="CJ3" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CK3" s="2" t="inlineStr"/>
+      <c r="CK3" s="2" t="inlineStr">
+        <is>
+          <t>1A/1B 馆区域有展商反映馆内个别点位灯光偏暗；受交通管控要求（2 号门限行），对观众进出会产生一定影响；两日简餐的菜都偏咸。</t>
+        </is>
+      </c>
       <c r="CL3" s="2" t="inlineStr"/>
       <c r="CM3" s="2" t="inlineStr"/>
       <c r="CN3" s="2" t="inlineStr"/>
       <c r="CO3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:38:19</t>
+          <t>2026-10-09 11:51:24</t>
         </is>
       </c>
       <c r="CP3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:38:19</t>
-        </is>
-      </c>
-      <c r="CQ3" s="2" t="inlineStr">
-        <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b711521938c54f69a2377a7cb15ad1b1.mp3</t>
-        </is>
-      </c>
-      <c r="CR3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 分 45 秒 </t>
-        </is>
-      </c>
-      <c r="CS3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 14:36:31</t>
-        </is>
-      </c>
+          <t>2026-10-09 11:51:24</t>
+        </is>
+      </c>
+      <c r="CQ3" s="2" t="inlineStr"/>
+      <c r="CR3" s="2" t="inlineStr"/>
+      <c r="CS3" s="2" t="inlineStr"/>
       <c r="CT3" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2534,26 +2702,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV3" s="2" t="inlineStr">
-        <is>
-          <t>0,323,324,326</t>
-        </is>
-      </c>
+      <c r="CV3" s="2" t="inlineStr"/>
       <c r="CW3" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX3" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市萧山区盈丰街道帆影路杭州棋院(智力大厦)棋类馆</t>
-        </is>
-      </c>
-      <c r="CY3" s="2" t="inlineStr">
-        <is>
-          <t>杭博访问员2</t>
-        </is>
-      </c>
+      <c r="CX3" s="2" t="inlineStr"/>
+      <c r="CY3" s="2" t="inlineStr"/>
       <c r="CZ3" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -2573,7 +2729,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2588,36 +2744,48 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>动漫周边</t>
+          <t>2026 第三届中国（杭州）国际日化及卫生用品产业博览会</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>参展商</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2-4次</t>
-        </is>
-      </c>
+          <t>展览主承办</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5001-10000人</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2627,12 +2795,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -2647,8 +2815,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2661,7 +2837,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -2669,26 +2845,58 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2696,22 +2904,22 @@
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AP4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR4" s="2" t="inlineStr">
@@ -2719,14 +2927,46 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AT4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AX4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AY4" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AZ4" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
       <c r="BA4" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2734,21 +2974,37 @@
       </c>
       <c r="BB4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr"/>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr"/>
-      <c r="BF4" s="2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BC4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BD4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BE4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BG4" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI4" s="2" t="inlineStr">
@@ -2778,19 +3034,11 @@
       </c>
       <c r="BN4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BO4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BP4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BO4" s="2" t="inlineStr"/>
+      <c r="BP4" s="2" t="inlineStr"/>
       <c r="BQ4" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -2821,31 +3069,39 @@
       <c r="CB4" s="2" t="inlineStr"/>
       <c r="CC4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="CD4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">超出预期	</t>
-        </is>
-      </c>
-      <c r="CE4" s="2" t="inlineStr"/>
-      <c r="CF4" s="2" t="inlineStr"/>
+          <t>未达到预期</t>
+        </is>
+      </c>
+      <c r="CE4" s="2" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="CF4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="CG4" s="2" t="inlineStr"/>
-      <c r="CH4" s="2" t="inlineStr"/>
-      <c r="CI4" s="2" t="inlineStr">
+      <c r="CH4" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
+      <c r="CI4" s="2" t="inlineStr"/>
       <c r="CJ4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CK4" s="2" t="inlineStr">
         <is>
-          <t>空调温度可以低一点</t>
+          <t>布撤展车辆通行证办理流程繁琐，办证需加盖三枚印章；办证经办人离岗/下班导致无法办理、通行证难按时办结；场内叉车收费过高，布撤展整体手续繁杂；餐饮价格偏高（面）。</t>
         </is>
       </c>
       <c r="CL4" s="2" t="inlineStr"/>
@@ -2853,29 +3109,17 @@
       <c r="CN4" s="2" t="inlineStr"/>
       <c r="CO4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:34:26</t>
+          <t>2026-10-09 11:45:06</t>
         </is>
       </c>
       <c r="CP4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:34:26</t>
-        </is>
-      </c>
-      <c r="CQ4" s="2" t="inlineStr">
-        <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/f38ade3ea237486981e0f55861e91efa.mp3</t>
-        </is>
-      </c>
-      <c r="CR4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 分 17 秒 </t>
-        </is>
-      </c>
-      <c r="CS4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 14:31:07</t>
-        </is>
-      </c>
+          <t>2026-10-09 11:45:06</t>
+        </is>
+      </c>
+      <c r="CQ4" s="2" t="inlineStr"/>
+      <c r="CR4" s="2" t="inlineStr"/>
+      <c r="CS4" s="2" t="inlineStr"/>
       <c r="CT4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2886,26 +3130,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV4" s="2" t="inlineStr">
-        <is>
-          <t>0,323,324,326</t>
-        </is>
-      </c>
+      <c r="CV4" s="2" t="inlineStr"/>
       <c r="CW4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX4" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市萧山区盈丰街道帆影路奥景名邸</t>
-        </is>
-      </c>
-      <c r="CY4" s="2" t="inlineStr">
-        <is>
-          <t>杭博访问员2</t>
-        </is>
-      </c>
+      <c r="CX4" s="2" t="inlineStr"/>
+      <c r="CY4" s="2" t="inlineStr"/>
       <c r="CZ4" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -2925,7 +3157,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2940,36 +3172,48 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>动漫周边</t>
+          <t>CHPE第九届（杭州）国际时尚发制品博览会</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>参展商</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+          <t>展览主承办</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5001-10000人</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>首次</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18-25岁</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2979,19 +3223,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2999,11 +3243,19 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -3021,26 +3273,58 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -3071,14 +3355,46 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AY5" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AZ5" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
       <c r="BA5" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -3089,18 +3405,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BC5" s="2" t="inlineStr"/>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr"/>
-      <c r="BF5" s="2" t="inlineStr"/>
+      <c r="BC5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BD5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BE5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BG5" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI5" s="2" t="inlineStr">
@@ -3133,16 +3465,8 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BO5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BP5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="BO5" s="2" t="inlineStr"/>
+      <c r="BP5" s="2" t="inlineStr"/>
       <c r="BQ5" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -3173,23 +3497,31 @@
       <c r="CB5" s="2" t="inlineStr"/>
       <c r="CC5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CD5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">超出预期	</t>
-        </is>
-      </c>
-      <c r="CE5" s="2" t="inlineStr"/>
-      <c r="CF5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">达到预期	</t>
+        </is>
+      </c>
+      <c r="CE5" s="2" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="CF5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="CG5" s="2" t="inlineStr"/>
-      <c r="CH5" s="2" t="inlineStr"/>
-      <c r="CI5" s="2" t="inlineStr">
+      <c r="CH5" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
+      <c r="CI5" s="2" t="inlineStr"/>
       <c r="CJ5" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -3197,7 +3529,7 @@
       </c>
       <c r="CK5" s="2" t="inlineStr">
         <is>
-          <t>1F空调温度调低一点</t>
+          <t>对于初次来办的展商，缺乏足够的引导和提醒；电箱主线线径相比其他同规格产品偏小，标称负载与实际可承载功率存在差距，易引发跳闸；场馆广播系统效果较差，仅缺少开闭馆定时播报功能；简餐餐品定价偏高；场内动线复杂，多展同期举办时入口封闭管理会影响通行效率；地下停车场通往展馆内部缺少清晰的公共导引标识；货运通行证办理存在不便，办证地点较远，车证价格高。</t>
         </is>
       </c>
       <c r="CL5" s="2" t="inlineStr"/>
@@ -3205,29 +3537,17 @@
       <c r="CN5" s="2" t="inlineStr"/>
       <c r="CO5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:25:01</t>
+          <t>2026-10-09 11:29:30</t>
         </is>
       </c>
       <c r="CP5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:25:01</t>
-        </is>
-      </c>
-      <c r="CQ5" s="2" t="inlineStr">
-        <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/dcd65288a23a40ae8f859a7126f27c79.mp3</t>
-        </is>
-      </c>
-      <c r="CR5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 分 43 秒 </t>
-        </is>
-      </c>
-      <c r="CS5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 14:22:14</t>
-        </is>
-      </c>
+          <t>2026-10-09 11:29:30</t>
+        </is>
+      </c>
+      <c r="CQ5" s="2" t="inlineStr"/>
+      <c r="CR5" s="2" t="inlineStr"/>
+      <c r="CS5" s="2" t="inlineStr"/>
       <c r="CT5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3238,26 +3558,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV5" s="2" t="inlineStr">
-        <is>
-          <t>0,323,324,326</t>
-        </is>
-      </c>
+      <c r="CV5" s="2" t="inlineStr"/>
       <c r="CW5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX5" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市萧山区盈丰街道帆影路智力大厦</t>
-        </is>
-      </c>
-      <c r="CY5" s="2" t="inlineStr">
-        <is>
-          <t>杭博访问员2</t>
-        </is>
-      </c>
+      <c r="CX5" s="2" t="inlineStr"/>
+      <c r="CY5" s="2" t="inlineStr"/>
       <c r="CZ5" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -3277,7 +3585,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3304,7 +3612,7 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2-4次</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3314,7 +3622,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18-25岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -3547,33 +3855,37 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK6" s="2" t="inlineStr"/>
+      <c r="CK6" s="2" t="inlineStr">
+        <is>
+          <t>空调温度可以调低一点</t>
+        </is>
+      </c>
       <c r="CL6" s="2" t="inlineStr"/>
       <c r="CM6" s="2" t="inlineStr"/>
       <c r="CN6" s="2" t="inlineStr"/>
       <c r="CO6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:21:59</t>
+          <t>2026-09-30 14:53:15</t>
         </is>
       </c>
       <c r="CP6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:21:59</t>
+          <t>2026-09-30 14:53:15</t>
         </is>
       </c>
       <c r="CQ6" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/70f172c42bc44cf28967cfc89fc1198d.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/150c94ad48da4b219dfdee6302e5c38b.mp3</t>
         </is>
       </c>
       <c r="CR6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 20 秒 </t>
+          <t xml:space="preserve">4 分 15 秒 </t>
         </is>
       </c>
       <c r="CS6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:19:37</t>
+          <t>2026-09-30 14:48:58</t>
         </is>
       </c>
       <c r="CT6" s="2" t="inlineStr">
@@ -3598,7 +3910,7 @@
       </c>
       <c r="CX6" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道帆影路智力大厦</t>
+          <t>浙江省杭州市萧山区盈丰街道利一路奥景名邸</t>
         </is>
       </c>
       <c r="CY6" s="2" t="inlineStr">
@@ -3625,7 +3937,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3652,7 +3964,7 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2-4次</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3768,7 +4080,7 @@
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS7" s="2" t="inlineStr"/>
@@ -3901,27 +4213,27 @@
       <c r="CN7" s="2" t="inlineStr"/>
       <c r="CO7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:18:43</t>
+          <t>2026-09-30 14:38:19</t>
         </is>
       </c>
       <c r="CP7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:18:43</t>
+          <t>2026-09-30 14:38:19</t>
         </is>
       </c>
       <c r="CQ7" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/497fe3ea38cd430d9e3b4cb86c963d26.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b711521938c54f69a2377a7cb15ad1b1.mp3</t>
         </is>
       </c>
       <c r="CR7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 1 秒 </t>
+          <t xml:space="preserve">1 分 45 秒 </t>
         </is>
       </c>
       <c r="CS7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15:39</t>
+          <t>2026-09-30 14:36:31</t>
         </is>
       </c>
       <c r="CT7" s="2" t="inlineStr">
@@ -3973,7 +4285,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4000,7 +4312,7 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2-4次</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4010,7 +4322,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18-25岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -4027,12 +4339,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -4243,33 +4555,37 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK8" s="2" t="inlineStr"/>
+      <c r="CK8" s="2" t="inlineStr">
+        <is>
+          <t>空调温度可以低一点</t>
+        </is>
+      </c>
       <c r="CL8" s="2" t="inlineStr"/>
       <c r="CM8" s="2" t="inlineStr"/>
       <c r="CN8" s="2" t="inlineStr"/>
       <c r="CO8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15:23</t>
+          <t>2026-09-30 14:34:26</t>
         </is>
       </c>
       <c r="CP8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15:23</t>
+          <t>2026-09-30 14:34:26</t>
         </is>
       </c>
       <c r="CQ8" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/8496f7c3e9df41418a72ef77941fe6ca.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/f38ade3ea237486981e0f55861e91efa.mp3</t>
         </is>
       </c>
       <c r="CR8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 47 秒 </t>
+          <t xml:space="preserve">3 分 17 秒 </t>
         </is>
       </c>
       <c r="CS8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:12:33</t>
+          <t>2026-09-30 14:31:07</t>
         </is>
       </c>
       <c r="CT8" s="2" t="inlineStr">
@@ -4321,7 +4637,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4348,17 +4664,17 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2-4次</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>18-25岁</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -4591,33 +4907,37 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK9" s="2" t="inlineStr"/>
+      <c r="CK9" s="2" t="inlineStr">
+        <is>
+          <t>1F空调温度调低一点</t>
+        </is>
+      </c>
       <c r="CL9" s="2" t="inlineStr"/>
       <c r="CM9" s="2" t="inlineStr"/>
       <c r="CN9" s="2" t="inlineStr"/>
       <c r="CO9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:11:51</t>
+          <t>2026-09-30 14:25:01</t>
         </is>
       </c>
       <c r="CP9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:11:51</t>
+          <t>2026-09-30 14:25:01</t>
         </is>
       </c>
       <c r="CQ9" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4a93a9bd8b0b4c169b5e4932bae7e80d.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/dcd65288a23a40ae8f859a7126f27c79.mp3</t>
         </is>
       </c>
       <c r="CR9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 7 秒 </t>
+          <t xml:space="preserve">2 分 43 秒 </t>
         </is>
       </c>
       <c r="CS9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:08:41</t>
+          <t>2026-09-30 14:22:14</t>
         </is>
       </c>
       <c r="CT9" s="2" t="inlineStr">
@@ -4642,7 +4962,7 @@
       </c>
       <c r="CX9" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道博奥路奥景名邸</t>
+          <t>浙江省杭州市萧山区盈丰街道帆影路智力大厦</t>
         </is>
       </c>
       <c r="CY9" s="2" t="inlineStr">
@@ -4669,7 +4989,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4701,12 +5021,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>18-25岁</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -4735,12 +5055,12 @@
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr"/>
@@ -4939,37 +5259,33 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK10" s="2" t="inlineStr">
-        <is>
-          <t>几号门和几号门的标识标牌不突出</t>
-        </is>
-      </c>
+      <c r="CK10" s="2" t="inlineStr"/>
       <c r="CL10" s="2" t="inlineStr"/>
       <c r="CM10" s="2" t="inlineStr"/>
       <c r="CN10" s="2" t="inlineStr"/>
       <c r="CO10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:07:37</t>
+          <t>2026-09-30 14:21:59</t>
         </is>
       </c>
       <c r="CP10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:07:37</t>
+          <t>2026-09-30 14:21:59</t>
         </is>
       </c>
       <c r="CQ10" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/5e45d26d84de4e00bce366f83a8cb963.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/70f172c42bc44cf28967cfc89fc1198d.mp3</t>
         </is>
       </c>
       <c r="CR10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 4 秒 </t>
+          <t xml:space="preserve">2 分 20 秒 </t>
         </is>
       </c>
       <c r="CS10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:04:31</t>
+          <t>2026-09-30 14:19:37</t>
         </is>
       </c>
       <c r="CT10" s="2" t="inlineStr">
@@ -4994,7 +5310,7 @@
       </c>
       <c r="CX10" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道利一路奥景名邸</t>
+          <t>浙江省杭州市萧山区盈丰街道帆影路智力大厦</t>
         </is>
       </c>
       <c r="CY10" s="2" t="inlineStr">
@@ -5021,7 +5337,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -5164,7 +5480,7 @@
       </c>
       <c r="AR11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AS11" s="2" t="inlineStr"/>
@@ -5297,27 +5613,27 @@
       <c r="CN11" s="2" t="inlineStr"/>
       <c r="CO11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:04:04</t>
+          <t>2026-09-30 14:18:43</t>
         </is>
       </c>
       <c r="CP11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:04:04</t>
+          <t>2026-09-30 14:18:43</t>
         </is>
       </c>
       <c r="CQ11" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/559802edebcc4f2cbd7532b29f2d0efb.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/497fe3ea38cd430d9e3b4cb86c963d26.mp3</t>
         </is>
       </c>
       <c r="CR11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 46 秒 </t>
+          <t xml:space="preserve">3 分 1 秒 </t>
         </is>
       </c>
       <c r="CS11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:01:15</t>
+          <t>2026-09-30 14:15:39</t>
         </is>
       </c>
       <c r="CT11" s="2" t="inlineStr">
@@ -5342,7 +5658,7 @@
       </c>
       <c r="CX11" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道利一路奥景名邸</t>
+          <t>浙江省杭州市萧山区盈丰街道帆影路杭州棋院(智力大厦)棋类馆</t>
         </is>
       </c>
       <c r="CY11" s="2" t="inlineStr">
@@ -5369,7 +5685,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5423,24 +5739,24 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
@@ -5639,37 +5955,33 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK12" s="2" t="inlineStr">
-        <is>
-          <t>标识不清晰</t>
-        </is>
-      </c>
+      <c r="CK12" s="2" t="inlineStr"/>
       <c r="CL12" s="2" t="inlineStr"/>
       <c r="CM12" s="2" t="inlineStr"/>
       <c r="CN12" s="2" t="inlineStr"/>
       <c r="CO12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:59:01</t>
+          <t>2026-09-30 14:15:23</t>
         </is>
       </c>
       <c r="CP12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:59:01</t>
+          <t>2026-09-30 14:15:23</t>
         </is>
       </c>
       <c r="CQ12" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/bb53d95ae4564849818647735ac9d5c9.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/8496f7c3e9df41418a72ef77941fe6ca.mp3</t>
         </is>
       </c>
       <c r="CR12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 分 20 秒 </t>
+          <t xml:space="preserve">2 分 47 秒 </t>
         </is>
       </c>
       <c r="CS12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:54:38</t>
+          <t>2026-09-30 14:12:33</t>
         </is>
       </c>
       <c r="CT12" s="2" t="inlineStr">
@@ -5694,7 +6006,7 @@
       </c>
       <c r="CX12" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州棋院(智力大厦)棋类馆奥景名邸</t>
+          <t>浙江省杭州市萧山区盈丰街道帆影路奥景名邸</t>
         </is>
       </c>
       <c r="CY12" s="2" t="inlineStr">
@@ -5721,7 +6033,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -5736,7 +6048,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>动漫周边</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -5753,7 +6065,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5787,12 +6099,12 @@
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr"/>
@@ -5991,37 +6303,33 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK13" s="2" t="inlineStr">
-        <is>
-          <t>指引再清晰一点</t>
-        </is>
-      </c>
+      <c r="CK13" s="2" t="inlineStr"/>
       <c r="CL13" s="2" t="inlineStr"/>
       <c r="CM13" s="2" t="inlineStr"/>
       <c r="CN13" s="2" t="inlineStr"/>
       <c r="CO13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:37:17</t>
+          <t>2026-09-30 14:11:51</t>
         </is>
       </c>
       <c r="CP13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:37:17</t>
+          <t>2026-09-30 14:11:51</t>
         </is>
       </c>
       <c r="CQ13" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/9d8924e592d844d1be1e551b56b9f1f2.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4a93a9bd8b0b4c169b5e4932bae7e80d.mp3</t>
         </is>
       </c>
       <c r="CR13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 38 秒 </t>
+          <t xml:space="preserve">3 分 7 秒 </t>
         </is>
       </c>
       <c r="CS13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:33:36</t>
+          <t>2026-09-30 14:08:41</t>
         </is>
       </c>
       <c r="CT13" s="2" t="inlineStr">
@@ -6046,7 +6354,7 @@
       </c>
       <c r="CX13" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道奥颂迪贝雅医疗美容(旗舰门诊部)万象世界中心</t>
+          <t>浙江省杭州市萧山区盈丰街道博奥路奥景名邸</t>
         </is>
       </c>
       <c r="CY13" s="2" t="inlineStr">
@@ -6073,7 +6381,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -6088,7 +6396,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>日化</t>
+          <t>动漫周边</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6105,7 +6413,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6117,7 +6425,7 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6127,24 +6435,24 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr"/>
@@ -6229,12 +6537,12 @@
       <c r="AZ14" s="2" t="inlineStr"/>
       <c r="BA14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BC14" s="2" t="inlineStr"/>
@@ -6243,12 +6551,12 @@
       <c r="BF14" s="2" t="inlineStr"/>
       <c r="BG14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BI14" s="2" t="inlineStr">
@@ -6263,7 +6571,7 @@
       </c>
       <c r="BK14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL14" s="2" t="inlineStr">
@@ -6278,17 +6586,17 @@
       </c>
       <c r="BN14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BO14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BQ14" s="2" t="inlineStr">
@@ -6321,12 +6629,12 @@
       <c r="CB14" s="2" t="inlineStr"/>
       <c r="CC14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="CD14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">达到预期	</t>
+          <t xml:space="preserve">超出预期	</t>
         </is>
       </c>
       <c r="CE14" s="2" t="inlineStr"/>
@@ -6340,12 +6648,12 @@
       </c>
       <c r="CJ14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="CK14" s="2" t="inlineStr">
         <is>
-          <t>3B展厅空调太冷；美食廊排队轮到了说要去其他处买餐券才能买饭；出口只出不进，去吃饭需要重新绕一圈进安检，很麻烦。</t>
+          <t>几号门和几号门的标识标牌不突出</t>
         </is>
       </c>
       <c r="CL14" s="2" t="inlineStr"/>
@@ -6353,17 +6661,29 @@
       <c r="CN14" s="2" t="inlineStr"/>
       <c r="CO14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:36:43</t>
+          <t>2026-09-30 14:07:37</t>
         </is>
       </c>
       <c r="CP14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:36:43</t>
-        </is>
-      </c>
-      <c r="CQ14" s="2" t="inlineStr"/>
-      <c r="CR14" s="2" t="inlineStr"/>
-      <c r="CS14" s="2" t="inlineStr"/>
+          <t>2026-09-30 14:07:37</t>
+        </is>
+      </c>
+      <c r="CQ14" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/5e45d26d84de4e00bce366f83a8cb963.mp3</t>
+        </is>
+      </c>
+      <c r="CR14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 4 秒 </t>
+        </is>
+      </c>
+      <c r="CS14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:04:31</t>
+        </is>
+      </c>
       <c r="CT14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -6374,14 +6694,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV14" s="2" t="inlineStr"/>
+      <c r="CV14" s="2" t="inlineStr">
+        <is>
+          <t>0,323,324,326</t>
+        </is>
+      </c>
       <c r="CW14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX14" s="2" t="inlineStr"/>
-      <c r="CY14" s="2" t="inlineStr"/>
+      <c r="CX14" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道利一路奥景名邸</t>
+        </is>
+      </c>
+      <c r="CY14" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
       <c r="CZ14" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -6401,7 +6733,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -6416,48 +6748,36 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CHPE 第九届（杭州）国际时尚发制品博览会</t>
+          <t>动漫周边</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>展览主承办</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>5001-10000人</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+          <t>参展商</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>首次</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6467,19 +6787,19 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -6487,19 +6807,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -6509,7 +6821,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -6517,58 +6829,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
-      <c r="AD15" s="2" t="inlineStr"/>
-      <c r="AE15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AL15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -6599,46 +6879,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AT15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AV15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AW15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AX15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AY15" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AZ15" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr"/>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
       <c r="BA15" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -6649,34 +6897,18 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BC15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BD15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BE15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="BC15" s="2" t="inlineStr"/>
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr"/>
+      <c r="BF15" s="2" t="inlineStr"/>
       <c r="BG15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BI15" s="2" t="inlineStr">
@@ -6709,8 +6941,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BO15" s="2" t="inlineStr"/>
-      <c r="BP15" s="2" t="inlineStr"/>
+      <c r="BO15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BP15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BQ15" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -6741,57 +6981,57 @@
       <c r="CB15" s="2" t="inlineStr"/>
       <c r="CC15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="CD15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">达到预期	</t>
-        </is>
-      </c>
-      <c r="CE15" s="2" t="inlineStr">
-        <is>
-          <t>比较满意</t>
-        </is>
-      </c>
-      <c r="CF15" s="2" t="inlineStr">
+          <t xml:space="preserve">超出预期	</t>
+        </is>
+      </c>
+      <c r="CE15" s="2" t="inlineStr"/>
+      <c r="CF15" s="2" t="inlineStr"/>
+      <c r="CG15" s="2" t="inlineStr"/>
+      <c r="CH15" s="2" t="inlineStr"/>
+      <c r="CI15" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CG15" s="2" t="inlineStr"/>
-      <c r="CH15" s="2" t="inlineStr">
+      <c r="CJ15" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CI15" s="2" t="inlineStr"/>
-      <c r="CJ15" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="CK15" s="2" t="inlineStr">
-        <is>
-          <t>对于初次来办的展商，缺乏足够的引导和提醒；电箱主线线径相比其他同规格产品偏小，标称负载与实际可承载功率存在差距，易引发跳闸；场馆广播系统效果较差，仅缺少开闭馆定时播报功能；简餐餐品定价偏高；场内动线复杂，多展同期举办时入口封闭管理会影响通行效率；地下停车场通往展馆内部缺少清晰的公共导引标识；货运通行证办理存在不便，办证地点较远，车证价格高。</t>
-        </is>
-      </c>
+      <c r="CK15" s="2" t="inlineStr"/>
       <c r="CL15" s="2" t="inlineStr"/>
       <c r="CM15" s="2" t="inlineStr"/>
       <c r="CN15" s="2" t="inlineStr"/>
       <c r="CO15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:30:53</t>
+          <t>2026-09-30 14:04:04</t>
         </is>
       </c>
       <c r="CP15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:30:53</t>
-        </is>
-      </c>
-      <c r="CQ15" s="2" t="inlineStr"/>
-      <c r="CR15" s="2" t="inlineStr"/>
-      <c r="CS15" s="2" t="inlineStr"/>
+          <t>2026-09-30 14:04:04</t>
+        </is>
+      </c>
+      <c r="CQ15" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/559802edebcc4f2cbd7532b29f2d0efb.mp3</t>
+        </is>
+      </c>
+      <c r="CR15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 46 秒 </t>
+        </is>
+      </c>
+      <c r="CS15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:01:15</t>
+        </is>
+      </c>
       <c r="CT15" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -6802,14 +7042,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV15" s="2" t="inlineStr"/>
+      <c r="CV15" s="2" t="inlineStr">
+        <is>
+          <t>0,323,324,326</t>
+        </is>
+      </c>
       <c r="CW15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX15" s="2" t="inlineStr"/>
-      <c r="CY15" s="2" t="inlineStr"/>
+      <c r="CX15" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道利一路奥景名邸</t>
+        </is>
+      </c>
+      <c r="CY15" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
       <c r="CZ15" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -6829,7 +7081,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6844,48 +7096,36 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026 第三届中国（杭州）国际日化及卫生用品产业博览会</t>
+          <t>动漫周边</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>展览主承办</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5001-10000人</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+          <t>参展商</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>首次</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>18-25岁</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6895,36 +7135,28 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -6937,7 +7169,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -6945,58 +7177,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
-      <c r="AD16" s="2" t="inlineStr"/>
-      <c r="AE16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AL16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -7004,22 +7204,22 @@
       </c>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AP16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AQ16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR16" s="2" t="inlineStr">
@@ -7027,46 +7227,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AT16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AV16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AX16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AY16" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AZ16" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
       <c r="BA16" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -7077,34 +7245,18 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BC16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BD16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BE16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="BC16" s="2" t="inlineStr"/>
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr"/>
+      <c r="BF16" s="2" t="inlineStr"/>
       <c r="BG16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BI16" s="2" t="inlineStr">
@@ -7134,11 +7286,19 @@
       </c>
       <c r="BN16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BO16" s="2" t="inlineStr"/>
-      <c r="BP16" s="2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BO16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BP16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BQ16" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -7169,39 +7329,31 @@
       <c r="CB16" s="2" t="inlineStr"/>
       <c r="CC16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="CD16" s="2" t="inlineStr">
         <is>
-          <t>未达到预期</t>
-        </is>
-      </c>
-      <c r="CE16" s="2" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="CF16" s="2" t="inlineStr">
+          <t xml:space="preserve">超出预期	</t>
+        </is>
+      </c>
+      <c r="CE16" s="2" t="inlineStr"/>
+      <c r="CF16" s="2" t="inlineStr"/>
+      <c r="CG16" s="2" t="inlineStr"/>
+      <c r="CH16" s="2" t="inlineStr"/>
+      <c r="CI16" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CG16" s="2" t="inlineStr"/>
-      <c r="CH16" s="2" t="inlineStr">
+      <c r="CJ16" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CI16" s="2" t="inlineStr"/>
-      <c r="CJ16" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="CK16" s="2" t="inlineStr">
         <is>
-          <t>布撤展车辆通行证办理流程繁琐，办证需加盖三枚印章；办证经办人离岗/下班导致无法办理、通行证难按时办结；场内叉车收费过高，布撤展整体手续繁杂；餐饮价格偏高（面）。</t>
+          <t>标识不清晰</t>
         </is>
       </c>
       <c r="CL16" s="2" t="inlineStr"/>
@@ -7209,17 +7361,29 @@
       <c r="CN16" s="2" t="inlineStr"/>
       <c r="CO16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:07:11</t>
+          <t>2026-09-30 13:59:01</t>
         </is>
       </c>
       <c r="CP16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:07:11</t>
-        </is>
-      </c>
-      <c r="CQ16" s="2" t="inlineStr"/>
-      <c r="CR16" s="2" t="inlineStr"/>
-      <c r="CS16" s="2" t="inlineStr"/>
+          <t>2026-09-30 13:59:01</t>
+        </is>
+      </c>
+      <c r="CQ16" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/bb53d95ae4564849818647735ac9d5c9.mp3</t>
+        </is>
+      </c>
+      <c r="CR16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 分 20 秒 </t>
+        </is>
+      </c>
+      <c r="CS16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:54:38</t>
+        </is>
+      </c>
       <c r="CT16" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -7230,14 +7394,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV16" s="2" t="inlineStr"/>
+      <c r="CV16" s="2" t="inlineStr">
+        <is>
+          <t>0,323,324,326</t>
+        </is>
+      </c>
       <c r="CW16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX16" s="2" t="inlineStr"/>
-      <c r="CY16" s="2" t="inlineStr"/>
+      <c r="CX16" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州棋院(智力大厦)棋类馆奥景名邸</t>
+        </is>
+      </c>
+      <c r="CY16" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
       <c r="CZ16" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -7257,7 +7433,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -7272,48 +7448,36 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026第十七届国际生物发酵产品与技术装备展览会</t>
+          <t>新能源汽车</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>展览主承办</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10001人以上</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>首次</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>参展商</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2-4次</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7323,36 +7487,28 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -7373,58 +7529,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
-      <c r="AD17" s="2" t="inlineStr"/>
-      <c r="AE17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AL17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
+      <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -7432,7 +7556,7 @@
       </c>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO17" s="2" t="inlineStr">
@@ -7447,7 +7571,7 @@
       </c>
       <c r="AQ17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR17" s="2" t="inlineStr">
@@ -7455,46 +7579,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AT17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AV17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AW17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AX17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AY17" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AZ17" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
+      <c r="AS17" s="2" t="inlineStr"/>
+      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" s="2" t="inlineStr"/>
+      <c r="AX17" s="2" t="inlineStr"/>
+      <c r="AY17" s="2" t="inlineStr"/>
+      <c r="AZ17" s="2" t="inlineStr"/>
       <c r="BA17" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -7502,29 +7594,13 @@
       </c>
       <c r="BB17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BC17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BD17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BE17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BC17" s="2" t="inlineStr"/>
+      <c r="BD17" s="2" t="inlineStr"/>
+      <c r="BE17" s="2" t="inlineStr"/>
+      <c r="BF17" s="2" t="inlineStr"/>
       <c r="BG17" s="2" t="inlineStr">
         <is>
           <t>不涉及</t>
@@ -7552,21 +7628,29 @@
       </c>
       <c r="BL17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BM17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BO17" s="2" t="inlineStr"/>
-      <c r="BP17" s="2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BO17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BP17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BQ17" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -7597,39 +7681,31 @@
       <c r="CB17" s="2" t="inlineStr"/>
       <c r="CC17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="CD17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">达到预期	</t>
-        </is>
-      </c>
-      <c r="CE17" s="2" t="inlineStr">
-        <is>
-          <t>比较满意</t>
-        </is>
-      </c>
-      <c r="CF17" s="2" t="inlineStr">
+          <t xml:space="preserve">超出预期	</t>
+        </is>
+      </c>
+      <c r="CE17" s="2" t="inlineStr"/>
+      <c r="CF17" s="2" t="inlineStr"/>
+      <c r="CG17" s="2" t="inlineStr"/>
+      <c r="CH17" s="2" t="inlineStr"/>
+      <c r="CI17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CG17" s="2" t="inlineStr"/>
-      <c r="CH17" s="2" t="inlineStr">
+      <c r="CJ17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CI17" s="2" t="inlineStr"/>
-      <c r="CJ17" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="CK17" s="2" t="inlineStr">
         <is>
-          <t>对接过程缺少主动提醒、沟通响应不及时；4.展厅内部动线较为混乱，同期展会展位密集，出入口多，访客难以找到准确的安检口；货运通道门洞偏窄、高度不足，车辆进场作业速度慢，整体货运效率偏低。</t>
+          <t>指引再清晰一点</t>
         </is>
       </c>
       <c r="CL17" s="2" t="inlineStr"/>
@@ -7637,17 +7713,29 @@
       <c r="CN17" s="2" t="inlineStr"/>
       <c r="CO17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00:27</t>
+          <t>2026-09-30 13:37:17</t>
         </is>
       </c>
       <c r="CP17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00:27</t>
-        </is>
-      </c>
-      <c r="CQ17" s="2" t="inlineStr"/>
-      <c r="CR17" s="2" t="inlineStr"/>
-      <c r="CS17" s="2" t="inlineStr"/>
+          <t>2026-09-30 13:37:17</t>
+        </is>
+      </c>
+      <c r="CQ17" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/9d8924e592d844d1be1e551b56b9f1f2.mp3</t>
+        </is>
+      </c>
+      <c r="CR17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 38 秒 </t>
+        </is>
+      </c>
+      <c r="CS17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:33:36</t>
+        </is>
+      </c>
       <c r="CT17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -7658,14 +7746,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="CV17" s="2" t="inlineStr"/>
+      <c r="CV17" s="2" t="inlineStr">
+        <is>
+          <t>0,323,324,326</t>
+        </is>
+      </c>
       <c r="CW17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CX17" s="2" t="inlineStr"/>
-      <c r="CY17" s="2" t="inlineStr"/>
+      <c r="CX17" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道奥颂迪贝雅医疗美容(旗舰门诊部)万象世界中心</t>
+        </is>
+      </c>
+      <c r="CY17" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
       <c r="CZ17" s="2" t="inlineStr">
         <is>
           <t>一期</t>
@@ -7685,7 +7785,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -7700,48 +7800,36 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026 浙江跨境电商产业带及区域合作展&amp;杭州出口跨境电商博览会</t>
+          <t>日化</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>展览主承办</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10001人以上</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5次以上</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>参展商</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7763,7 +7851,7 @@
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -7771,16 +7859,8 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -7793,166 +7873,86 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
-      <c r="AD18" s="2" t="inlineStr"/>
-      <c r="AE18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AL18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AM18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AN18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AO18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AP18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AQ18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AR18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AS18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AT18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AV18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AW18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AX18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AY18" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AZ18" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="BA18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BB18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BC18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BD18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BE18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BC18" s="2" t="inlineStr"/>
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr"/>
+      <c r="BF18" s="2" t="inlineStr"/>
       <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -7975,26 +7975,34 @@
       </c>
       <c r="BK18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BL18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BN18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BM18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BN18" s="2" t="inlineStr">
+      <c r="BO18" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BO18" s="2" t="inlineStr"/>
-      <c r="BP18" s="2" t="inlineStr"/>
+      <c r="BP18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="BQ18" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -8033,31 +8041,23 @@
           <t xml:space="preserve">达到预期	</t>
         </is>
       </c>
-      <c r="CE18" s="2" t="inlineStr">
-        <is>
-          <t>比较满意</t>
-        </is>
-      </c>
-      <c r="CF18" s="2" t="inlineStr">
+      <c r="CE18" s="2" t="inlineStr"/>
+      <c r="CF18" s="2" t="inlineStr"/>
+      <c r="CG18" s="2" t="inlineStr"/>
+      <c r="CH18" s="2" t="inlineStr"/>
+      <c r="CI18" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CG18" s="2" t="inlineStr"/>
-      <c r="CH18" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="CI18" s="2" t="inlineStr"/>
       <c r="CJ18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CK18" s="2" t="inlineStr">
         <is>
-          <t>地下车库标识标牌需要增设；场馆网 络收费价格偏高；商务简餐口味一般且定价偏高。</t>
+          <t>3B展厅空调太冷；美食廊排队轮到了说要去其他处买餐券才能买饭；出口只出不进，去吃饭需要重新绕一圈进安检，很麻烦。</t>
         </is>
       </c>
       <c r="CL18" s="2" t="inlineStr"/>
@@ -8065,12 +8065,12 @@
       <c r="CN18" s="2" t="inlineStr"/>
       <c r="CO18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:51:01</t>
+          <t>2026-09-30 10:36:43</t>
         </is>
       </c>
       <c r="CP18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:51:01</t>
+          <t>2026-09-30 10:36:43</t>
         </is>
       </c>
       <c r="CQ18" s="2" t="inlineStr"/>
@@ -8113,7 +8113,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>第 22 届浙江国际医疗设备展览会暨创新技术交流会</t>
+          <t>2026第十七届国际生物发酵产品与技术装备展览会</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5次以上</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AG19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AH19" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="AK19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL19" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AO19" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AQ19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR19" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AS19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AT19" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AU19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AV19" s="2" t="inlineStr">
@@ -8333,44 +8333,44 @@
       </c>
       <c r="AW19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AY19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AZ19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BA19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BC19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AX19" s="2" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AY19" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AZ19" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="BA19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BB19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BC19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BD19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -8408,17 +8408,17 @@
       </c>
       <c r="BL19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BM19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BN19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BO19" s="2" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
       <c r="CB19" s="2" t="inlineStr"/>
       <c r="CC19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CD19" s="2" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="CK19" s="2" t="inlineStr">
         <is>
-          <t>申报环节所需提交的材料数量较多；各展厅内地沟盖板因使用年久，大部分盖板出现翘起、不稳定的现象，存在安全隐患；散场时段打车困难。</t>
+          <t>对接过程缺少主动提醒、沟通响应不及时；展厅内部动线较为混乱，同期展会展位密集，出入口多，访客难以找到准确的安检口；货运通道门洞偏窄、高度不足，车辆进场作业速度慢，整体货运效率偏低。</t>
         </is>
       </c>
       <c r="CL19" s="2" t="inlineStr"/>
@@ -8493,12 +8493,12 @@
       <c r="CN19" s="2" t="inlineStr"/>
       <c r="CO19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:13:52</t>
+          <t>2026-09-29 10:00:27</t>
         </is>
       </c>
       <c r="CP19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:13:52</t>
+          <t>2026-09-29 10:00:27</t>
         </is>
       </c>
       <c r="CQ19" s="2" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>AI show2026杭州国际人工智能应用与机器人创新博览会</t>
+          <t>第 22 届浙江国际医疗设备展览会暨创新技术交流会</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5001-10000人</t>
+          <t>10001人以上</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2-4次</t>
+          <t>5次以上</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -8582,22 +8582,22 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8612,14 +8612,14 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8634,14 +8634,14 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -8681,94 +8681,94 @@
       </c>
       <c r="AG20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AS20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AT20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AX20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AH20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AL20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AM20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AN20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AO20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AP20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AQ20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AR20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AS20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AT20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AV20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AW20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AX20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="AY20" s="2" t="inlineStr">
         <is>
           <t>不涉及</t>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="BG20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BI20" s="2" t="inlineStr">
@@ -8881,17 +8881,17 @@
       <c r="CB20" s="2" t="inlineStr"/>
       <c r="CC20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD20" s="2" t="inlineStr">
         <is>
-          <t>未达到预期</t>
+          <t xml:space="preserve">达到预期	</t>
         </is>
       </c>
       <c r="CE20" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>比较满意</t>
         </is>
       </c>
       <c r="CF20" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       <c r="CI20" s="2" t="inlineStr"/>
       <c r="CJ20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="CK20" s="2" t="inlineStr">
         <is>
-          <t>餐饮口味一般，二期场馆内部动线复杂，不好找，一期通往二期的指引标识不够清晰。</t>
+          <t>申报环节所需提交的材料数量较多；各展厅内地沟盖板因使用年久，大部分盖板出现翘起、不稳定的现象，存在安全隐患；散场时段打车困难。</t>
         </is>
       </c>
       <c r="CL20" s="2" t="inlineStr"/>
@@ -8921,12 +8921,12 @@
       <c r="CN20" s="2" t="inlineStr"/>
       <c r="CO20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:51:25</t>
+          <t>2026-09-28 15:13:52</t>
         </is>
       </c>
       <c r="CP20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:51:25</t>
+          <t>2026-09-28 15:13:52</t>
         </is>
       </c>
       <c r="CQ20" s="2" t="inlineStr"/>
@@ -8952,7 +8952,7 @@
       <c r="CY20" s="2" t="inlineStr"/>
       <c r="CZ20" s="2" t="inlineStr">
         <is>
-          <t>二期</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="DA20" s="4" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -8984,21 +8984,25 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>日化</t>
+          <t>AI show2026杭州国际人工智能应用与机器人创新博览会</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>参展商</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>首次</t>
-        </is>
-      </c>
+          <t>展览主承办</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5001-10000人</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2-4次</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>男</t>
@@ -9009,11 +9013,19 @@
           <t>36-45岁</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9028,14 +9040,14 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -9043,8 +9055,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -9057,7 +9077,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -9065,26 +9085,58 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr"/>
-      <c r="AF21" s="2" t="inlineStr"/>
-      <c r="AG21" s="2" t="inlineStr"/>
-      <c r="AH21" s="2" t="inlineStr"/>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="inlineStr"/>
-      <c r="AK21" s="2" t="inlineStr"/>
-      <c r="AL21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AM21" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -9092,12 +9144,12 @@
       </c>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AO21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AP21" s="2" t="inlineStr">
@@ -9107,7 +9159,7 @@
       </c>
       <c r="AQ21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR21" s="2" t="inlineStr">
@@ -9115,14 +9167,46 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS21" s="2" t="inlineStr"/>
-      <c r="AT21" s="2" t="inlineStr"/>
-      <c r="AU21" s="2" t="inlineStr"/>
-      <c r="AV21" s="2" t="inlineStr"/>
-      <c r="AW21" s="2" t="inlineStr"/>
-      <c r="AX21" s="2" t="inlineStr"/>
-      <c r="AY21" s="2" t="inlineStr"/>
-      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="AS21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AY21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AZ21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
       <c r="BA21" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -9133,18 +9217,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BC21" s="2" t="inlineStr"/>
-      <c r="BD21" s="2" t="inlineStr"/>
-      <c r="BE21" s="2" t="inlineStr"/>
-      <c r="BF21" s="2" t="inlineStr"/>
+      <c r="BC21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BD21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BE21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BG21" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI21" s="2" t="inlineStr">
@@ -9177,16 +9277,8 @@
           <t>10</t>
         </is>
       </c>
-      <c r="BO21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BP21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="BO21" s="2" t="inlineStr"/>
+      <c r="BP21" s="2" t="inlineStr"/>
       <c r="BQ21" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -9217,31 +9309,39 @@
       <c r="CB21" s="2" t="inlineStr"/>
       <c r="CC21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="CD21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">达到预期	</t>
-        </is>
-      </c>
-      <c r="CE21" s="2" t="inlineStr"/>
-      <c r="CF21" s="2" t="inlineStr"/>
+          <t>未达到预期</t>
+        </is>
+      </c>
+      <c r="CE21" s="2" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="CF21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="CG21" s="2" t="inlineStr"/>
-      <c r="CH21" s="2" t="inlineStr"/>
-      <c r="CI21" s="2" t="inlineStr">
+      <c r="CH21" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
+      <c r="CI21" s="2" t="inlineStr"/>
       <c r="CJ21" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CK21" s="2" t="inlineStr">
         <is>
-          <t>场馆设施和服务好，但是人流量不多。</t>
+          <t>餐饮口味一般，二期场馆内部动线复杂，不好找，一期通往二期的指引标识不够清晰。</t>
         </is>
       </c>
       <c r="CL21" s="2" t="inlineStr"/>
@@ -9249,12 +9349,12 @@
       <c r="CN21" s="2" t="inlineStr"/>
       <c r="CO21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:20:38</t>
+          <t>2026-09-28 14:51:25</t>
         </is>
       </c>
       <c r="CP21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:20:38</t>
+          <t>2026-09-28 14:51:25</t>
         </is>
       </c>
       <c r="CQ21" s="2" t="inlineStr"/>
@@ -9280,7 +9380,7 @@
       <c r="CY21" s="2" t="inlineStr"/>
       <c r="CZ21" s="2" t="inlineStr">
         <is>
-          <t>一期</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="DA21" s="4" t="inlineStr">
@@ -9297,7 +9397,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9375,7 +9475,7 @@
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -9385,7 +9485,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -9569,7 +9669,7 @@
       </c>
       <c r="CK22" s="2" t="inlineStr">
         <is>
-          <t>VIP3B-02左侧（靠展厅大门）通道门前5~6m的位置有点盖松动，踩踏会翘起。</t>
+          <t>场馆设施和服务好，但是人流量不多。</t>
         </is>
       </c>
       <c r="CL22" s="2" t="inlineStr"/>
@@ -9577,12 +9677,12 @@
       <c r="CN22" s="2" t="inlineStr"/>
       <c r="CO22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:13:09</t>
+          <t>2026-09-24 15:20:38</t>
         </is>
       </c>
       <c r="CP22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:13:09</t>
+          <t>2026-09-24 15:20:38</t>
         </is>
       </c>
       <c r="CQ22" s="2" t="inlineStr"/>
@@ -9625,7 +9725,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -9657,19 +9757,19 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9684,14 +9784,14 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9703,7 +9803,7 @@
       <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
@@ -9725,12 +9825,12 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" s="2" t="inlineStr"/>
@@ -9743,17 +9843,17 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AP23" s="2" t="inlineStr">
@@ -9763,7 +9863,7 @@
       </c>
       <c r="AQ23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR23" s="2" t="inlineStr">
@@ -9835,7 +9935,7 @@
       </c>
       <c r="BO23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP23" s="2" t="inlineStr">
@@ -9892,12 +9992,12 @@
       </c>
       <c r="CJ23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="CK23" s="2" t="inlineStr">
         <is>
-          <t>停车场没有指示牌；布展和开展走的不是一个出入口，没有指示，绕一大圈才走到安检口，很麻烦。另外希望可以有一个茶水间。</t>
+          <t>VIP3B-02左侧（靠展厅大门）通道门前5~6m的位置有点盖松动，踩踏会翘起。</t>
         </is>
       </c>
       <c r="CL23" s="2" t="inlineStr"/>
@@ -9905,12 +10005,12 @@
       <c r="CN23" s="2" t="inlineStr"/>
       <c r="CO23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:09:09</t>
+          <t>2026-09-24 15:13:09</t>
         </is>
       </c>
       <c r="CP23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:09:09</t>
+          <t>2026-09-24 15:13:09</t>
         </is>
       </c>
       <c r="CQ23" s="2" t="inlineStr"/>
@@ -9953,7 +10053,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -9985,19 +10085,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10012,14 +10112,14 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -10041,7 +10141,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -10053,7 +10153,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -10071,17 +10171,17 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AO24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AP24" s="2" t="inlineStr">
@@ -10091,7 +10191,7 @@
       </c>
       <c r="AQ24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR24" s="2" t="inlineStr">
@@ -10163,7 +10263,7 @@
       </c>
       <c r="BO24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BP24" s="2" t="inlineStr">
@@ -10225,7 +10325,7 @@
       </c>
       <c r="CK24" s="2" t="inlineStr">
         <is>
-          <t>人流量少；场馆附近拥堵。</t>
+          <t>停车场没有指示牌；布展和开展走的不是一个出入口，没有指示，绕一大圈才走到安检口，很麻烦。另外希望可以有一个茶水间。</t>
         </is>
       </c>
       <c r="CL24" s="2" t="inlineStr"/>
@@ -10233,12 +10333,12 @@
       <c r="CN24" s="2" t="inlineStr"/>
       <c r="CO24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:03:40</t>
+          <t>2026-09-24 15:09:09</t>
         </is>
       </c>
       <c r="CP24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:03:40</t>
+          <t>2026-09-24 15:09:09</t>
         </is>
       </c>
       <c r="CQ24" s="2" t="inlineStr"/>
@@ -10281,7 +10381,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -10313,7 +10413,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10325,7 +10425,7 @@
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10340,14 +10440,14 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -10369,7 +10469,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -10386,7 +10486,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE25" s="2" t="inlineStr"/>
@@ -10409,7 +10509,7 @@
       </c>
       <c r="AO25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AP25" s="2" t="inlineStr">
@@ -10419,7 +10519,7 @@
       </c>
       <c r="AQ25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR25" s="2" t="inlineStr">
@@ -10442,7 +10542,7 @@
       </c>
       <c r="BB25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BC25" s="2" t="inlineStr"/>
@@ -10451,12 +10551,12 @@
       <c r="BF25" s="2" t="inlineStr"/>
       <c r="BG25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BI25" s="2" t="inlineStr">
@@ -10471,7 +10571,7 @@
       </c>
       <c r="BK25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL25" s="2" t="inlineStr">
@@ -10481,7 +10581,7 @@
       </c>
       <c r="BM25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN25" s="2" t="inlineStr">
@@ -10491,12 +10591,12 @@
       </c>
       <c r="BO25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP25" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BQ25" s="2" t="inlineStr">
@@ -10529,12 +10629,12 @@
       <c r="CB25" s="2" t="inlineStr"/>
       <c r="CC25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD25" s="2" t="inlineStr">
         <is>
-          <t>未达到预期</t>
+          <t xml:space="preserve">达到预期	</t>
         </is>
       </c>
       <c r="CE25" s="2" t="inlineStr"/>
@@ -10543,17 +10643,17 @@
       <c r="CH25" s="2" t="inlineStr"/>
       <c r="CI25" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="CJ25" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="CJ25" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="CK25" s="2" t="inlineStr">
         <is>
-          <t>人流量差，办展效果不好；2楼饭菜难吃，而且三楼下去需要绕一大圈才能回来。</t>
+          <t>人流量少；场馆附近拥堵。</t>
         </is>
       </c>
       <c r="CL25" s="2" t="inlineStr"/>
@@ -10561,12 +10661,12 @@
       <c r="CN25" s="2" t="inlineStr"/>
       <c r="CO25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:01:03</t>
+          <t>2026-09-24 15:03:40</t>
         </is>
       </c>
       <c r="CP25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:01:03</t>
+          <t>2026-09-24 15:03:40</t>
         </is>
       </c>
       <c r="CQ25" s="2" t="inlineStr"/>
@@ -10609,7 +10709,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -10636,7 +10736,7 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2-4次</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10653,7 +10753,7 @@
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10668,14 +10768,14 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -10737,7 +10837,7 @@
       </c>
       <c r="AO26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AP26" s="2" t="inlineStr">
@@ -10770,7 +10870,7 @@
       </c>
       <c r="BB26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BC26" s="2" t="inlineStr"/>
@@ -10779,12 +10879,12 @@
       <c r="BF26" s="2" t="inlineStr"/>
       <c r="BG26" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI26" s="2" t="inlineStr">
@@ -10799,19 +10899,19 @@
       </c>
       <c r="BK26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM26" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BL26" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BM26" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BN26" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -10819,12 +10919,12 @@
       </c>
       <c r="BO26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BP26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BQ26" s="2" t="inlineStr">
@@ -10857,7 +10957,7 @@
       <c r="CB26" s="2" t="inlineStr"/>
       <c r="CC26" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="CD26" s="2" t="inlineStr">
@@ -10871,7 +10971,7 @@
       <c r="CH26" s="2" t="inlineStr"/>
       <c r="CI26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CJ26" s="2" t="inlineStr">
@@ -10881,7 +10981,7 @@
       </c>
       <c r="CK26" s="2" t="inlineStr">
         <is>
-          <t>内部动线封闭，多个展同时进行很乱，找不到出入口；场馆内部应该开放人流流通，不仅展商难找到准确的展位，顾客也找不到，整体统筹不好，而且制度死板，需要优化。</t>
+          <t>人流量差，办展效果不好；2楼饭菜难吃，而且三楼下去需要绕一大圈才能回来。</t>
         </is>
       </c>
       <c r="CL26" s="2" t="inlineStr"/>
@@ -10889,12 +10989,12 @@
       <c r="CN26" s="2" t="inlineStr"/>
       <c r="CO26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:57:58</t>
+          <t>2026-09-24 15:01:03</t>
         </is>
       </c>
       <c r="CP26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:57:58</t>
+          <t>2026-09-24 15:01:03</t>
         </is>
       </c>
       <c r="CQ26" s="2" t="inlineStr"/>
@@ -10937,7 +11037,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -10964,7 +11064,7 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2-4次</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -10974,14 +11074,14 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10991,12 +11091,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -11025,7 +11125,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -11075,7 +11175,7 @@
       </c>
       <c r="AQ27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR27" s="2" t="inlineStr">
@@ -11117,22 +11217,22 @@
       </c>
       <c r="BI27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BJ27" s="2" t="inlineStr">
         <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BK27" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BL27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BM27" s="2" t="inlineStr">
@@ -11142,12 +11242,12 @@
       </c>
       <c r="BN27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BO27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP27" s="2" t="inlineStr">
@@ -11185,12 +11285,12 @@
       <c r="CB27" s="2" t="inlineStr"/>
       <c r="CC27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CD27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">达到预期	</t>
+          <t>未达到预期</t>
         </is>
       </c>
       <c r="CE27" s="2" t="inlineStr"/>
@@ -11204,21 +11304,25 @@
       </c>
       <c r="CJ27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="CK27" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="CK27" s="2" t="inlineStr">
+        <is>
+          <t>内部动线封闭，多个展同时进行很乱，找不到出入口；场馆内部应该开放人流流通，不仅展商难找到准确的展位，顾客也找不到，整体统筹不好，而且制度死板，需要优化。</t>
+        </is>
+      </c>
       <c r="CL27" s="2" t="inlineStr"/>
       <c r="CM27" s="2" t="inlineStr"/>
       <c r="CN27" s="2" t="inlineStr"/>
       <c r="CO27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:44:29</t>
+          <t>2026-09-24 14:57:58</t>
         </is>
       </c>
       <c r="CP27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:44:29</t>
+          <t>2026-09-24 14:57:58</t>
         </is>
       </c>
       <c r="CQ27" s="2" t="inlineStr"/>
@@ -11261,7 +11365,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -11293,12 +11397,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -11315,19 +11419,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -11354,7 +11458,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
@@ -11366,7 +11470,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE28" s="2" t="inlineStr"/>
@@ -11384,7 +11488,7 @@
       </c>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO28" s="2" t="inlineStr">
@@ -11441,12 +11545,12 @@
       </c>
       <c r="BI28" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BJ28" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BK28" s="2" t="inlineStr">
@@ -11466,12 +11570,12 @@
       </c>
       <c r="BN28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BO28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BP28" s="2" t="inlineStr">
@@ -11528,25 +11632,21 @@
       </c>
       <c r="CJ28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="CK28" s="2" t="inlineStr">
-        <is>
-          <t>人流量少</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="CK28" s="2" t="inlineStr"/>
       <c r="CL28" s="2" t="inlineStr"/>
       <c r="CM28" s="2" t="inlineStr"/>
       <c r="CN28" s="2" t="inlineStr"/>
       <c r="CO28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:41:24</t>
+          <t>2026-09-24 14:44:29</t>
         </is>
       </c>
       <c r="CP28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:41:24</t>
+          <t>2026-09-24 14:44:29</t>
         </is>
       </c>
       <c r="CQ28" s="2" t="inlineStr"/>
@@ -11589,7 +11689,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -11604,7 +11704,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>发制品</t>
+          <t>日化</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -11626,7 +11726,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -11667,7 +11767,7 @@
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
@@ -11677,12 +11777,12 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
@@ -11694,7 +11794,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE29" s="2" t="inlineStr"/>
@@ -11712,7 +11812,7 @@
       </c>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AO29" s="2" t="inlineStr">
@@ -11745,7 +11845,7 @@
       <c r="AZ29" s="2" t="inlineStr"/>
       <c r="BA29" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB29" s="2" t="inlineStr">
@@ -11784,7 +11884,7 @@
       </c>
       <c r="BL29" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BM29" s="2" t="inlineStr">
@@ -11856,12 +11956,12 @@
       </c>
       <c r="CJ29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CK29" s="2" t="inlineStr">
         <is>
-          <t>电梯有点少，人多的时候运行很慢。（直梯）</t>
+          <t>人流量少</t>
         </is>
       </c>
       <c r="CL29" s="2" t="inlineStr"/>
@@ -11869,12 +11969,12 @@
       <c r="CN29" s="2" t="inlineStr"/>
       <c r="CO29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:54:27</t>
+          <t>2026-09-24 14:41:24</t>
         </is>
       </c>
       <c r="CP29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:54:27</t>
+          <t>2026-09-24 14:41:24</t>
         </is>
       </c>
       <c r="CQ29" s="2" t="inlineStr"/>
@@ -11917,7 +12017,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -11949,7 +12049,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11961,7 +12061,7 @@
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11983,7 +12083,7 @@
       <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -11995,7 +12095,7 @@
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
@@ -12017,7 +12117,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -12078,7 +12178,7 @@
       </c>
       <c r="BB30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BC30" s="2" t="inlineStr"/>
@@ -12127,12 +12227,12 @@
       </c>
       <c r="BO30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BQ30" s="2" t="inlineStr">
@@ -12184,12 +12284,12 @@
       </c>
       <c r="CJ30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="CK30" s="2" t="inlineStr">
         <is>
-          <t>标识牌不清晰，找展位找了半小时；3C展厅靠里的位置灯光不够亮；多个展一起进行，比较混乱，顾客找不到，要绕很久。</t>
+          <t>电梯有点少，人多的时候运行很慢。（直梯）</t>
         </is>
       </c>
       <c r="CL30" s="2" t="inlineStr"/>
@@ -12197,12 +12297,12 @@
       <c r="CN30" s="2" t="inlineStr"/>
       <c r="CO30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:50:48</t>
+          <t>2026-09-23 09:54:27</t>
         </is>
       </c>
       <c r="CP30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:50:48</t>
+          <t>2026-09-23 09:54:27</t>
         </is>
       </c>
       <c r="CQ30" s="2" t="inlineStr"/>
@@ -12245,7 +12345,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -12272,12 +12372,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2-4次</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12289,12 +12389,12 @@
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -12316,14 +12416,14 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr"/>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
@@ -12345,7 +12445,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -12401,12 +12501,12 @@
       <c r="AZ31" s="2" t="inlineStr"/>
       <c r="BA31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BC31" s="2" t="inlineStr"/>
@@ -12415,52 +12515,52 @@
       <c r="BF31" s="2" t="inlineStr"/>
       <c r="BG31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr">
         <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BJ31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BN31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BO31" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BI31" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="BJ31" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="BK31" s="2" t="inlineStr">
+      <c r="BP31" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="BL31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BM31" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BN31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BO31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BP31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="BQ31" s="2" t="inlineStr">
@@ -12493,7 +12593,7 @@
       <c r="CB31" s="2" t="inlineStr"/>
       <c r="CC31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD31" s="2" t="inlineStr">
@@ -12517,7 +12617,7 @@
       </c>
       <c r="CK31" s="2" t="inlineStr">
         <is>
-          <t>外围太堵；停车场没有标识牌，应该在停车场设置醒目的标识；路线安排不合理，需要绕一大圈才能走到安检口；3C展厅断电了一次；餐饮价格偏高口味一般；三楼男厕所很脏。</t>
+          <t>标识牌不清晰，找展位找了半小时；3C展厅靠里的位置灯光不够亮；多个展一起进行，比较混乱，顾客找不到，要绕很久。</t>
         </is>
       </c>
       <c r="CL31" s="2" t="inlineStr"/>
@@ -12525,12 +12625,12 @@
       <c r="CN31" s="2" t="inlineStr"/>
       <c r="CO31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45:59</t>
+          <t>2026-09-23 09:50:48</t>
         </is>
       </c>
       <c r="CP31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45:59</t>
+          <t>2026-09-23 09:50:48</t>
         </is>
       </c>
       <c r="CQ31" s="2" t="inlineStr"/>
@@ -12573,7 +12673,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -12600,7 +12700,7 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2-4次</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -12610,14 +12710,14 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12639,12 +12739,12 @@
       <c r="R32" s="2" t="inlineStr"/>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
@@ -12661,7 +12761,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -12743,12 +12843,12 @@
       <c r="BF32" s="2" t="inlineStr"/>
       <c r="BG32" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BI32" s="2" t="inlineStr">
@@ -12763,7 +12863,7 @@
       </c>
       <c r="BK32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BL32" s="2" t="inlineStr">
@@ -12773,7 +12873,7 @@
       </c>
       <c r="BM32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BN32" s="2" t="inlineStr">
@@ -12783,12 +12883,12 @@
       </c>
       <c r="BO32" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP32" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BQ32" s="2" t="inlineStr">
@@ -12821,7 +12921,7 @@
       <c r="CB32" s="2" t="inlineStr"/>
       <c r="CC32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CD32" s="2" t="inlineStr">
@@ -12840,21 +12940,25 @@
       </c>
       <c r="CJ32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="CK32" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="CK32" s="2" t="inlineStr">
+        <is>
+          <t>外围太堵；停车场没有标识牌，应该在停车场设置醒目的标识；路线安排不合理，需要绕一大圈才能走到安检口；3C展厅断电了一次；餐饮价格偏高口味一般；三楼男厕所很脏。</t>
+        </is>
+      </c>
       <c r="CL32" s="2" t="inlineStr"/>
       <c r="CM32" s="2" t="inlineStr"/>
       <c r="CN32" s="2" t="inlineStr"/>
       <c r="CO32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:36:15</t>
+          <t>2026-09-23 09:45:59</t>
         </is>
       </c>
       <c r="CP32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:36:15</t>
+          <t>2026-09-23 09:45:59</t>
         </is>
       </c>
       <c r="CQ32" s="2" t="inlineStr"/>
@@ -12897,7 +13001,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -12941,12 +13045,12 @@
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -13058,7 +13162,7 @@
       </c>
       <c r="BB33" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BC33" s="2" t="inlineStr"/>
@@ -13107,12 +13211,12 @@
       </c>
       <c r="BO33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BP33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BQ33" s="2" t="inlineStr">
@@ -13173,12 +13277,12 @@
       <c r="CN33" s="2" t="inlineStr"/>
       <c r="CO33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:33:37</t>
+          <t>2026-09-23 09:36:15</t>
         </is>
       </c>
       <c r="CP33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:33:37</t>
+          <t>2026-09-23 09:36:15</t>
         </is>
       </c>
       <c r="CQ33" s="2" t="inlineStr"/>
@@ -13221,7 +13325,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -13253,12 +13357,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -13275,19 +13379,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -13339,32 +13443,32 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AP34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AQ34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS34" s="2" t="inlineStr"/>
@@ -13382,7 +13486,7 @@
       </c>
       <c r="BB34" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BC34" s="2" t="inlineStr"/>
@@ -13431,12 +13535,12 @@
       </c>
       <c r="BO34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP34" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BQ34" s="2" t="inlineStr">
@@ -13469,7 +13573,7 @@
       <c r="CB34" s="2" t="inlineStr"/>
       <c r="CC34" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="CD34" s="2" t="inlineStr">
@@ -13491,22 +13595,18 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK34" s="2" t="inlineStr">
-        <is>
-          <t>厕所马桶太多，蹲坑只有两个；打车过来要走很远，标识牌不清晰，难找</t>
-        </is>
-      </c>
+      <c r="CK34" s="2" t="inlineStr"/>
       <c r="CL34" s="2" t="inlineStr"/>
       <c r="CM34" s="2" t="inlineStr"/>
       <c r="CN34" s="2" t="inlineStr"/>
       <c r="CO34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:44:50</t>
+          <t>2026-09-23 09:33:37</t>
         </is>
       </c>
       <c r="CP34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:44:50</t>
+          <t>2026-09-23 09:33:37</t>
         </is>
       </c>
       <c r="CQ34" s="2" t="inlineStr"/>
@@ -13549,7 +13649,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -13564,7 +13664,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>生物发酵</t>
+          <t>发制品</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -13581,7 +13681,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13593,7 +13693,7 @@
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13603,7 +13703,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -13615,7 +13715,7 @@
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -13667,32 +13767,32 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AP35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AQ35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AR35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AS35" s="2" t="inlineStr"/>
@@ -13705,12 +13805,12 @@
       <c r="AZ35" s="2" t="inlineStr"/>
       <c r="BA35" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BB35" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BC35" s="2" t="inlineStr"/>
@@ -13759,12 +13859,12 @@
       </c>
       <c r="BO35" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BP35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BQ35" s="2" t="inlineStr">
@@ -13821,7 +13921,7 @@
       </c>
       <c r="CK35" s="2" t="inlineStr">
         <is>
-          <t>场馆附近很堵，里面有点绕，标识牌只有在靠近展厅的位置比较多。</t>
+          <t>厕所马桶太多，蹲坑只有两个；打车过来要走很远，标识牌不清晰，难找</t>
         </is>
       </c>
       <c r="CL35" s="2" t="inlineStr"/>
@@ -13829,12 +13929,12 @@
       <c r="CN35" s="2" t="inlineStr"/>
       <c r="CO35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:20:04</t>
+          <t>2026-09-22 16:44:50</t>
         </is>
       </c>
       <c r="CP35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:20:04</t>
+          <t>2026-09-22 16:44:50</t>
         </is>
       </c>
       <c r="CQ35" s="2" t="inlineStr"/>
@@ -13877,7 +13977,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -13914,14 +14014,14 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13931,7 +14031,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13943,7 +14043,7 @@
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -14038,7 +14138,7 @@
       </c>
       <c r="BB36" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BC36" s="2" t="inlineStr"/>
@@ -14087,7 +14187,7 @@
       </c>
       <c r="BO36" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BP36" s="2" t="inlineStr">
@@ -14144,21 +14244,25 @@
       </c>
       <c r="CJ36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="CK36" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="CK36" s="2" t="inlineStr">
+        <is>
+          <t>场馆附近很堵，里面有点绕，标识牌只有在靠近展厅的位置比较多。</t>
+        </is>
+      </c>
       <c r="CL36" s="2" t="inlineStr"/>
       <c r="CM36" s="2" t="inlineStr"/>
       <c r="CN36" s="2" t="inlineStr"/>
       <c r="CO36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:09:20</t>
+          <t>2026-09-22 16:20:04</t>
         </is>
       </c>
       <c r="CP36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:09:20</t>
+          <t>2026-09-22 16:20:04</t>
         </is>
       </c>
       <c r="CQ36" s="2" t="inlineStr"/>
@@ -14201,7 +14305,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -14238,14 +14342,14 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14306,7 +14410,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE37" s="2" t="inlineStr"/>
@@ -14357,7 +14461,7 @@
       <c r="AZ37" s="2" t="inlineStr"/>
       <c r="BA37" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BB37" s="2" t="inlineStr">
@@ -14449,7 +14553,7 @@
       <c r="CB37" s="2" t="inlineStr"/>
       <c r="CC37" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD37" s="2" t="inlineStr">
@@ -14468,25 +14572,21 @@
       </c>
       <c r="CJ37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="CK37" s="2" t="inlineStr">
-        <is>
-          <t>地铁走过来有点远</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="CK37" s="2" t="inlineStr"/>
       <c r="CL37" s="2" t="inlineStr"/>
       <c r="CM37" s="2" t="inlineStr"/>
       <c r="CN37" s="2" t="inlineStr"/>
       <c r="CO37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:04:50</t>
+          <t>2026-09-22 16:09:20</t>
         </is>
       </c>
       <c r="CP37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 16:04:50</t>
+          <t>2026-09-22 16:09:20</t>
         </is>
       </c>
       <c r="CQ37" s="2" t="inlineStr"/>
@@ -14529,7 +14629,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -14566,7 +14666,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -14583,12 +14683,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -14634,7 +14734,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE38" s="2" t="inlineStr"/>
@@ -14782,7 +14882,7 @@
       </c>
       <c r="CD38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">超出预期	</t>
+          <t xml:space="preserve">达到预期	</t>
         </is>
       </c>
       <c r="CE38" s="2" t="inlineStr"/>
@@ -14799,18 +14899,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK38" s="2" t="inlineStr"/>
+      <c r="CK38" s="2" t="inlineStr">
+        <is>
+          <t>地铁走过来有点远</t>
+        </is>
+      </c>
       <c r="CL38" s="2" t="inlineStr"/>
       <c r="CM38" s="2" t="inlineStr"/>
       <c r="CN38" s="2" t="inlineStr"/>
       <c r="CO38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:58:42</t>
+          <t>2026-09-22 16:04:50</t>
         </is>
       </c>
       <c r="CP38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:58:42</t>
+          <t>2026-09-22 16:04:50</t>
         </is>
       </c>
       <c r="CQ38" s="2" t="inlineStr"/>
@@ -14853,7 +14957,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -14897,7 +15001,7 @@
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14907,12 +15011,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -15123,22 +15227,18 @@
           <t>是</t>
         </is>
       </c>
-      <c r="CK39" s="2" t="inlineStr">
-        <is>
-          <t>吸烟区太少了，离展位远。</t>
-        </is>
-      </c>
+      <c r="CK39" s="2" t="inlineStr"/>
       <c r="CL39" s="2" t="inlineStr"/>
       <c r="CM39" s="2" t="inlineStr"/>
       <c r="CN39" s="2" t="inlineStr"/>
       <c r="CO39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:50:57</t>
+          <t>2026-09-22 15:58:42</t>
         </is>
       </c>
       <c r="CP39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:50:57</t>
+          <t>2026-09-22 15:58:42</t>
         </is>
       </c>
       <c r="CQ39" s="2" t="inlineStr"/>
@@ -15181,7 +15281,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -15213,24 +15313,24 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -15429,12 +15529,12 @@
       <c r="CB40" s="2" t="inlineStr"/>
       <c r="CC40" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="CD40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">达到预期	</t>
+          <t xml:space="preserve">超出预期	</t>
         </is>
       </c>
       <c r="CE40" s="2" t="inlineStr"/>
@@ -15448,12 +15548,12 @@
       </c>
       <c r="CJ40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="CK40" s="2" t="inlineStr">
         <is>
-          <t>出入口太少，出口太远，需要从1D走到1B。</t>
+          <t>吸烟区太少了，离展位远。</t>
         </is>
       </c>
       <c r="CL40" s="2" t="inlineStr"/>
@@ -15461,12 +15561,12 @@
       <c r="CN40" s="2" t="inlineStr"/>
       <c r="CO40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:45:26</t>
+          <t>2026-09-22 15:50:57</t>
         </is>
       </c>
       <c r="CP40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:45:26</t>
+          <t>2026-09-22 15:50:57</t>
         </is>
       </c>
       <c r="CQ40" s="2" t="inlineStr"/>
@@ -15509,7 +15609,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -15541,12 +15641,12 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -15558,17 +15658,17 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -15614,7 +15714,7 @@
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE41" s="2" t="inlineStr"/>
@@ -15627,32 +15727,32 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AP41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AQ41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS41" s="2" t="inlineStr"/>
@@ -15679,12 +15779,12 @@
       <c r="BF41" s="2" t="inlineStr"/>
       <c r="BG41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BI41" s="2" t="inlineStr">
@@ -15776,12 +15876,12 @@
       </c>
       <c r="CJ41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CK41" s="2" t="inlineStr">
         <is>
-          <t>动线安排不够合理，需要绕行。</t>
+          <t>出入口太少，出口太远，需要从1D走到1B。</t>
         </is>
       </c>
       <c r="CL41" s="2" t="inlineStr"/>
@@ -15789,12 +15889,12 @@
       <c r="CN41" s="2" t="inlineStr"/>
       <c r="CO41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:29:39</t>
+          <t>2026-09-22 15:45:26</t>
         </is>
       </c>
       <c r="CP41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:29:39</t>
+          <t>2026-09-22 15:45:26</t>
         </is>
       </c>
       <c r="CQ41" s="2" t="inlineStr"/>
@@ -15837,7 +15937,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -15874,7 +15974,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
@@ -15942,7 +16042,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE42" s="2" t="inlineStr"/>
@@ -15955,17 +16055,17 @@
       <c r="AL42" s="2" t="inlineStr"/>
       <c r="AM42" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AN42" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AO42" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AP42" s="2" t="inlineStr">
@@ -15975,12 +16075,12 @@
       </c>
       <c r="AQ42" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR42" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AS42" s="2" t="inlineStr"/>
@@ -16007,12 +16107,12 @@
       <c r="BF42" s="2" t="inlineStr"/>
       <c r="BG42" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BH42" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BI42" s="2" t="inlineStr">
@@ -16027,7 +16127,7 @@
       </c>
       <c r="BK42" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL42" s="2" t="inlineStr">
@@ -16109,7 +16209,7 @@
       </c>
       <c r="CK42" s="2" t="inlineStr">
         <is>
-          <t>工作人员不懂变通，展商每次都要刷身份证才能进入，拿外卖后不让从后门进入，必须得绕一大圈，很不合理。</t>
+          <t>动线安排不够合理，需要绕行。</t>
         </is>
       </c>
       <c r="CL42" s="2" t="inlineStr"/>
@@ -16117,12 +16217,12 @@
       <c r="CN42" s="2" t="inlineStr"/>
       <c r="CO42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:25:59</t>
+          <t>2026-09-22 15:29:39</t>
         </is>
       </c>
       <c r="CP42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:25:59</t>
+          <t>2026-09-22 15:29:39</t>
         </is>
       </c>
       <c r="CQ42" s="2" t="inlineStr"/>
@@ -16165,7 +16265,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -16209,7 +16309,7 @@
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -16219,12 +16319,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -16293,17 +16393,17 @@
       </c>
       <c r="AO43" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AP43" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ43" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR43" s="2" t="inlineStr">
@@ -16355,12 +16455,12 @@
       </c>
       <c r="BK43" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BL43" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BM43" s="2" t="inlineStr">
@@ -16370,7 +16470,7 @@
       </c>
       <c r="BN43" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BO43" s="2" t="inlineStr">
@@ -16432,12 +16532,12 @@
       </c>
       <c r="CJ43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="CK43" s="2" t="inlineStr">
         <is>
-          <t>由于安检要求，到处都围起来，绕了一大圈才能到展厅，特别不方便。</t>
+          <t>工作人员不懂变通，展商每次都要刷身份证才能进入，拿外卖后不让从后门进入，必须得绕一大圈，很不合理。</t>
         </is>
       </c>
       <c r="CL43" s="2" t="inlineStr"/>
@@ -16445,12 +16545,12 @@
       <c r="CN43" s="2" t="inlineStr"/>
       <c r="CO43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:05:12</t>
+          <t>2026-09-22 15:25:59</t>
         </is>
       </c>
       <c r="CP43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:05:12</t>
+          <t>2026-09-22 15:25:59</t>
         </is>
       </c>
       <c r="CQ43" s="2" t="inlineStr"/>
@@ -16493,7 +16593,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -16537,7 +16637,7 @@
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16547,19 +16647,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -16611,17 +16711,17 @@
       <c r="AL44" s="2" t="inlineStr"/>
       <c r="AM44" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AN44" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AP44" s="2" t="inlineStr">
@@ -16631,7 +16731,7 @@
       </c>
       <c r="AQ44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR44" s="2" t="inlineStr">
@@ -16673,22 +16773,22 @@
       </c>
       <c r="BI44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="BJ44" s="2" t="inlineStr">
         <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BK44" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BK44" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BL44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BM44" s="2" t="inlineStr">
@@ -16698,12 +16798,12 @@
       </c>
       <c r="BN44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BO44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP44" s="2" t="inlineStr">
@@ -16741,7 +16841,7 @@
       <c r="CB44" s="2" t="inlineStr"/>
       <c r="CC44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CD44" s="2" t="inlineStr">
@@ -16765,7 +16865,7 @@
       </c>
       <c r="CK44" s="2" t="inlineStr">
         <is>
-          <t>内部动线安排不合理，要出去拿外卖要绕一大圈，被工作人员拦住不让出去，服务态度不好。（1D门口这边）</t>
+          <t>由于安检要求，到处都围起来，绕了一大圈才能到展厅，特别不方便。</t>
         </is>
       </c>
       <c r="CL44" s="2" t="inlineStr"/>
@@ -16773,12 +16873,12 @@
       <c r="CN44" s="2" t="inlineStr"/>
       <c r="CO44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:56:46</t>
+          <t>2026-09-22 15:05:12</t>
         </is>
       </c>
       <c r="CP44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:56:46</t>
+          <t>2026-09-22 15:05:12</t>
         </is>
       </c>
       <c r="CQ44" s="2" t="inlineStr"/>
@@ -16821,7 +16921,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -16836,28 +16936,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2026 CBE 杭州国际美容博览会</t>
+          <t>生物发酵</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>展览主承办</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>10001人以上</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>2-4次</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t>参展商</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16865,16 +16961,8 @@
           <t>26-35岁</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -16899,7 +16987,7 @@
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -16907,101 +16995,61 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
       <c r="W45" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="inlineStr"/>
+      <c r="AL45" s="2" t="inlineStr"/>
+      <c r="AM45" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
-      <c r="AD45" s="2" t="inlineStr"/>
-      <c r="AE45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AL45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AM45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="AN45" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AO45" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AP45" s="2" t="inlineStr">
@@ -17011,7 +17059,7 @@
       </c>
       <c r="AQ45" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR45" s="2" t="inlineStr">
@@ -17019,118 +17067,78 @@
           <t>10</t>
         </is>
       </c>
-      <c r="AS45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AT45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AU45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AV45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AW45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AX45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AY45" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AZ45" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
+      <c r="AS45" s="2" t="inlineStr"/>
+      <c r="AT45" s="2" t="inlineStr"/>
+      <c r="AU45" s="2" t="inlineStr"/>
+      <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" s="2" t="inlineStr"/>
+      <c r="AX45" s="2" t="inlineStr"/>
+      <c r="AY45" s="2" t="inlineStr"/>
+      <c r="AZ45" s="2" t="inlineStr"/>
       <c r="BA45" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BB45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BC45" s="2" t="inlineStr"/>
+      <c r="BD45" s="2" t="inlineStr"/>
+      <c r="BE45" s="2" t="inlineStr"/>
+      <c r="BF45" s="2" t="inlineStr"/>
+      <c r="BG45" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BH45" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ45" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BB45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BC45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BD45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BE45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BG45" s="2" t="inlineStr">
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BN45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BO45" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BH45" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BI45" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="BJ45" s="2" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="BK45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BM45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BN45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BO45" s="2" t="inlineStr"/>
-      <c r="BP45" s="2" t="inlineStr"/>
+      <c r="BP45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="BQ45" s="2" t="inlineStr">
         <is>
           <t>不知道</t>
@@ -17161,7 +17169,7 @@
       <c r="CB45" s="2" t="inlineStr"/>
       <c r="CC45" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CD45" s="2" t="inlineStr">
@@ -17169,31 +17177,23 @@
           <t xml:space="preserve">达到预期	</t>
         </is>
       </c>
-      <c r="CE45" s="2" t="inlineStr">
-        <is>
-          <t>非常满意</t>
-        </is>
-      </c>
-      <c r="CF45" s="2" t="inlineStr">
+      <c r="CE45" s="2" t="inlineStr"/>
+      <c r="CF45" s="2" t="inlineStr"/>
+      <c r="CG45" s="2" t="inlineStr"/>
+      <c r="CH45" s="2" t="inlineStr"/>
+      <c r="CI45" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="CG45" s="2" t="inlineStr"/>
-      <c r="CH45" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="CI45" s="2" t="inlineStr"/>
       <c r="CJ45" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="CK45" s="2" t="inlineStr">
         <is>
-          <t>1A/1B 馆区域有展商反映馆内个别点位灯光偏暗；受交通管控要求（2 号门限行），对观众进出会产生一定影响；两日简餐的菜都偏咸。</t>
+          <t>内部动线安排不合理，要出去拿外卖要绕一大圈，被工作人员拦住不让出去，服务态度不好。（1D门口这边）</t>
         </is>
       </c>
       <c r="CL45" s="2" t="inlineStr"/>
@@ -17201,12 +17201,12 @@
       <c r="CN45" s="2" t="inlineStr"/>
       <c r="CO45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 10:06:05</t>
+          <t>2026-09-22 14:56:46</t>
         </is>
       </c>
       <c r="CP45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 10:06:05</t>
+          <t>2026-09-22 14:56:46</t>
         </is>
       </c>
       <c r="CQ45" s="2" t="inlineStr"/>
@@ -40281,7 +40281,7 @@
       </c>
       <c r="CK112" s="2" t="inlineStr">
         <is>
-          <t>应该做一个牌子引导游客去找</t>
+          <t>会长应该做一个牌子引导游客去找</t>
         </is>
       </c>
       <c r="CL112" s="2" t="inlineStr"/>
@@ -42544,7 +42544,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 美容博览会</t>
+          <t>美容博览会</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -42872,7 +42872,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 美容博览会</t>
+          <t>美容博览会</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -43200,7 +43200,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 美容博览会</t>
+          <t>美容博览会</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
